--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$F$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$F$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2269,53 +2269,73 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Тестовый товар — не публикуется</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862930/images/big/1.webp</t>
-        </is>
-      </c>
+          <t>Тестовая карточка для проверки автоматизации</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E/RE0F10A вариатора CVT, 4 шт NSK</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670858/670858043/images/big/1.webp</t>
+          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862930/images/big/1.webp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E/RE0F10A вариатора CVT, 4 шт NSK</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-32.wbbasket.ru/vol6708/part670858/670858043/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F60"/>
+  <autoFilter ref="A1:F61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2282,7 +2282,11 @@
           <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TESTWB001_1.jpg</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
     </row>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TESTWB001_1.jpg</t>
+          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TESTWB001_2.jpg</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$F$61</definedName>
@@ -482,12 +482,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий</t>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG6 02E305045 Новый улучшает теплоотвод отличное качество - проверенный!</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -554,23 +554,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла
-Уменьшает температуру масла КПП
-Резиновое кольцо в комплекте
-Алюминиевый корпус фильтра DSG6 DQ250 (02E305045)
-Надёжная замена OEM-пластика — предотвращает перегрев, трещины корпуса и продлевает срок службы DSG6.
-Артикул: 02E305045
-Совместимость: DSG6 02E (DQ250, мокрое сцепление), VW/Audi/Skoda/Seat (2004–2019)
-Преимущества:
-• Прочный алюминиевый корпус
-• Уплотнительное кольцо в комплекте
-Очень быстрая отправка
-Обновите корпус и убережёте DSG от перегрева</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -585,12 +574,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,12 +598,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1шт!</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -672,12 +661,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -696,22 +685,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW — артикул 0AM325219C
-Крышка поддона мехатроника. Устанавливается при обслуживании DSG7 (тип DQ200). Обеспечивает герметичность и защиту внутренних элементов.
-Назначение: крышка поддона мехатроника
-Совместимость: DSG7 DQ200, мехатроники 0AM / 0CW
-Артикул: 0AM325219C
-Преимущества:
-• Подходит для плановой замены
-• Простая установка без доработок
-• Надёжная защита от пыли и масла
-Очень быстрая отправка
-Возьмите сейчас — пригодится при обслуживании или замене поддона</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -730,12 +709,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -754,12 +733,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Новый фильтр dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Для чего нужен? Для ремонта мехатроника dsg 7 dq200 0am325025 0cw</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -778,13 +757,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 0AM</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 (артикул 0AM325443D) предназначена для герметичного соединения корпуса мехатроника на роботизированной коробке передач DSG 7 DQ 200 с  модификациями 0AM и 0CW. Усиленная прокладка используется при замене гидроблока, ревизии блока управления или устранении течи трансмиссионной жидкости.&lt;br/&gt;&lt;br/&gt;Подходит для большинства автомобилей VAG-группы (Volkswagen, Audi, Skoda, Seat), оснащённых трансмиссией DQ200. Обеспечивает надёжную герметизацию, изготовлена из термостойкого эластомера, рассчитанного на высокие нагрузки и температурные циклы.&lt;br/&gt;&lt;br/&gt;Прокладка 0AM325443D — один из ключевых элементов при ремонте мехатроника DSG 7.  Может поставляться как отдельно, так и в составе ремонтных комплектов.&lt;br/&gt;&lt;br/&gt;Прокладка для крышки мехатроника DSG7 DQ200 (0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Если у вас DQ200 то подойдет 100%. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.
-Значительно толще штатной и ходит намного дольше, заказывайте!</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -803,14 +781,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG cепараторная пластина мехатроника DSG7 DQ200</t>
+          <t>Оригинальная сепараторная пластина VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J
-Отличное качество VAG
-Не гнутая, ходит намного дольше аналогов, заказывайте оригинал VAG!</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -829,12 +805,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды DQ200 Hilti Контрактные проверенные на стенде&lt;br/&gt;&lt;br/&gt;Минимальный пробег оригинальных соленоидов DSG7 + проверка на стенде позволяют надежно решить проблему с вышедшеми из строя соленоидами 0am 0cw.&lt;br/&gt;&lt;br/&gt;Цена указана за 4 шт - 1 половинка как на фото (1 соленоид регулятор давления + 3 Shift Шифт соленоида) контрактные б/у минимальный пробег + каждый соленоид проверяется на стенде!&lt;br/&gt;&lt;br/&gt;Всего в мехатронике устанавливаются 8 шт - 2 половинки (2 соленоида регулятора давления + 6 соленоидов Shift Шифт)&lt;br/&gt;&lt;br/&gt;Внимание - соленоиды DQ 200 качественные проверенные на стенде, если вам нужно менять полный комплект соленоидов мехатроника 0AM 8 шт - заказывайте 2 половинки по 4 шт у нас. Соленоиды Hilti как на фото - ЕСЛИ У ВАС СТОЯТ СОЛЕНОИДЫ BOSCH (с коричневым соленоидом регулятором давления) МЕНЯТЬ НУЖНО КОМПЛЕКТ ЦЕЛИКОМ - 8 БОШ на 8 БОШ, либо 8 ХИЛТИ (как у нас) на 8 ХИЛТИ. Либо если у вас стоят ХИЛТИ и вы хотите поменять 4 шт на 4 шт - так тоже можно. Не нужно ставить 4 БОШ и 4 ХИЛТИ!</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -853,12 +829,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60бар).  Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CW Volkswagen, Audi, Skoda, Seat (2007–2023 и далее) Артикул: 0AM325587E Признаки износа/неисправности: Рывки при трогании с места Долгое задержание передач D/R Код ошибки (например, P0841) Появление металлической стружки в масле Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 Преимущества замены: Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока Отправка — максимально быстро Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -877,12 +853,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -901,26 +877,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
-Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Усиленная конструкция является надежной альтернативой пластиковому корпусу, рассчитана на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и их модификациях.
-Преимущества
-• Улучшенный отвод тепла — снижает рабочую температуру масла в КПП
-• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур
-• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек
-• Многократное использование при регламентном обслуживании
-• Оптимизированная форма с ребрами для повышения эффективности охлаждения
-Совместимость
-• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
-• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
-• Seat, Skoda с коробкой DQ500 (по каталогу)
-Номер детали
-0BH325183B
-Надёжная и долговечная деталь для вашей DSG7. Быстрая отправка.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -935,24 +897,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
-Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надежную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Анодированное красное покрытие дополнительно защищает металл от коррозии.
-Совместимость:
-• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
-• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
-• Seat, Skoda с коробкой DQ500 (по каталогу)
-Номер детали: 0BH325183B
-Особенности:
-• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам
-• Анодированное красное покрытие — защита от окисления и привлекательный внешний вид
-• Полная совместимость с оригинальными уплотнительными элементами
-• Повторно используемая конструкция
-Максимально быстрая отправка.</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1085,12 +1035,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 Плита сальники прокладки</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM325025</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 включает всё необходимое для ремонта и восстановления блока управления коробки передач. В комплект входят прокладка мехатроника DQ200, сальники, уплотнения, плита мехатроника и гидроплита. Совместим с трансмиссиями DSG 7 DQ200 0am и 0cw. Используется при замене гидроплиты, ремонте блока мехатроника (замене прокладок) или полной ревизии DSG. Ремкомплект подходит для большинства моделей VAG-группы (Volkswagen, Audi, Skoda, Seat) с коробкой DQ200. Детали высокого качества, проверенные временем. Прокладка крышки, комплект прокладок DSG 7, ремкомплект мехатроника купить — всё это вы найдёте в данном наборе.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1109,12 +1059,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1133,12 +1083,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальника 2 крышки</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльники крышки</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1200,43 +1150,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Каждый мехатроник DSG7 DQ200 проходит полную проверку на автомобиле после сборки.
-Мы не ограничиваемся стендовыми тестами — каждый мехатроник обязательно проходит обкатку на дороге, в реальных условиях эксплуатации. 
- • Каждый соленоид — оригинальный, проходит проверку на стенде
- • Тестирование выполняется с сопоставлением графиков с эталонными значениями, загруженными в систему
- • Любое отклонение — соленоид отбраковывается
-Используем
-Оригинальные запчасти VAG:
- • Крышка мехатроника
- • Сепараторная пластина под гидроплиту 0AM
- • Пластины соленоидов
- • Втулки штоков мехатроника DSG7 DQ200
-Усовершенствованные компоненты:
- • Усиленная прокладка крышки мехатроника (утолщенная, увеличенный ресурс)
- • Алюминиевые сальники толкателей вилок (высокое качество, не пластик и не дешевые аналоги)
- • Усиленные штоки DQ200 с дополнительной резинкой (повышенный срок службы)
- • Стальная вставка высокого качества+комплект надежных уплотнений (не теряют давление со временем)
- • Качественный ремкомплект прокладок мехатроника DSG7 DQ200
-Электронная часть:
- • Устанавливается качественная электронная плата 0AM927769D
- • Многолетний опыт производства и тестирования электронных компонентов
-Финальные испытания:
- • Каждый мехатроник проверяется на мини-стенде под давлением
- • Контроль времени сброса давления
- • Проверка работы толкателей и герметичности системы
-Главное преимущество — проверка на автомобиле:
-В отличие от большинства сервисов (99%), где мехатроник просто собирается и отдается клиенту, мы выполняем полноценную проверку DSG7 DQ200 в движении.
-Проверка на дороге — это:
- • работа всех систем под нагрузкой
- • реальное переключение передач
- • полноценная диагностика агрегата в сборе
-Только такой подход позволяет гарантировать, что мехатроник действительно исправен, а не «условно рабочий».
-Заказывайте восстановленные мехатроники DSG7 DQ200, полностью протестированные на авто, с оригинальными и улучшенными компонентами — по выгодной цене и с реальной гарантией работы.</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,12 +1174,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1323,21 +1242,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 + прокладка поддона dq200 набор</t>
+          <t>Оригинальная крышка + усиленная прокладка DSG7 DQ200</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОРИГИНАЛ VAG Крышка мехатроника DSG7 DQ200 (0AM325219C) + усиленная прокладка с утолщением мехатроника DQ200 DSG7(0AM325443D)
-Комплект для восстановления герметичности масляной крышки (поддона) при обслуживании мехатроника DSG7. Подходит для 7-ступенчатой коробки с сухим сцеплением (DQ200 всех модификаций).
-Артикулы: 0AM325219C + 0AM325443D
-Совместимость: DSG7 (DQ200, 7-ступ., сухое сцепление), 0AM / 0CW, VW/Audi/Skoda/Seat
-Преимущества:
-• Точный OEM-аналог без доработок
-• Устойчив к давлению и нагреву
-Очень быстрая отправка
-Набор пригодится при плановом обслуживании или замене крышки (поддона)
-Самый эффективный и качественный вариант - оригинал VAG + усовершенствованная прокладка - лучшее и самое надежное решение </t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1356,12 +1266,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7 шт.</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1380,22 +1290,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
-Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
-Все необходимые прокладки в ремкомплекте:
-Прокладка поддона
-Фильтр мехатроника 0AM325433E, 0AM325433B
-Пыльники штоков сцепления DSG7 DQ200 0AM, 0CW, 0AM325091F, 0AM325091E
-И так далее.
-Покупая наш ремонтный комплект гидроблока DSG7 0AM/0CW, вы выполняете полноценный ремонт мехатроника, меняя все расходники и устанавливая новую усиленную гидроплиту 0AM325066AE.
-Ошибки: P17BF, P189C, P0841, P1895
-Артикулы: 0AM325025D; 0AM325025DX; 0AM325025H; 0AM325025HX; 0AM325025L; 0AM325025LX; 0AM325025M; 0AM325025MX; 0AM325025K; 0AM325025N; 0AM325025R; 0AM325026A; 0AM325026C; 0AM325025DZSN; 0AM325025DZEM.
-Заказывайте!</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1414,16 +1314,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG пластины мехатроиника dsg7 dq200</t>
+          <t>Сепараторная пластина + пластины на соленоиды DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7 + пластины на соленоиды dsg7 
-Новые ОРИГИНАЛ VAG
-Напрямую с завода
-Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)
-Оригинал Volkswagen отличное качество, ходят намного дольше, не гнутые, заказывайте!</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1442,15 +1338,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Усиленный Новый поршень штока мехатроника DQ200 DSG 7 0AM 0CW
-Отличное качество - за счет усовершенствованной конструкции (доп резинки) ходит намного дольше
-Подходит на все штоки 0am325091E (101мм длинный) 0am325091F (99мм короткий)
-Продлите работу штоков и всего мехатроника в целом, заказывайте!</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1469,12 +1362,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1493,12 +1386,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
+          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1517,12 +1410,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1541,12 +1434,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1565,12 +1458,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Длинный шток 0AM325091E 101 мм+втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект длинный шток 101мм 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1589,27 +1482,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Короткий шток 0AM325091F 99 мм+втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект короткий шток 99мм 0AM325091F + DSG7 DQ200</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка
-Комплект: короткий шток сцепления 0AM325091F (99 мм) и гильза мехатроника DSG7 DQ200. Устраняет люфт и обеспечивает точную и надёжную работу сцепления.
-Совместимость:
-• DSG7 DQ200 (7-ступ., сухое сцепление)
-• VW / Audi / Skoda / Seat (до 2012 года)
-• Артикул штока: 0AM325091F
-Когда нужен:
-• Люфт или износ штока или втулки (гильзы)
-• Ошибки сцепления или гидроблока
-• Профилактика или ремонт мехатроника
-Особенности:
-• Шток 99 мм — точный заводской размер
-• Новая втулка — без повреждений
-• Отличное качество материалов
-Очень быстрая отправка
-Восстановите мехатроник сразу с ремкомплектом и без лишних затрат.</t>
+          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1688,12 +1566,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1712,12 +1590,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1736,12 +1614,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Сальник манжет штока сцепления мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1760,29 +1638,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 — 0AM325066AE / 0CW
-Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW) с увеличенной толщиной стенки. Обеспечивает стабильность давления и предотвращает ошибки P17BF/P1895 и другие при интенсивной эксплуатации.
-Совместимость:
-• DSG7 DQ200 (7-ступ., сухое сцепление)
-• VW, Audi, Skoda, Seat (2007–2025)
-• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C и другие. Устанавливается на мехатроники 0AM325025H и другие варианты, а также на мехатроники 0CW.
-Особенности:
-• Увеличенная толщина стенки в зоне гидроаккумулятора
-• Хорошее качество алюминия
-Очень быстрая отправка
-Решение для тех, кто хочет надёжность без риска ошибок и поломок DSG7.
-В описании использованы запросы: плита дсг; гидроплита dsg; гидроплита мехатроника; гидроплита дсг 7; плита dq200; гидроплита dq200; плита мехатроника dsg; гидроплита dsg 7 dq200; момент затяжки гидроплиты; усиленная плита мехатроника dq200; 0am325066ae; усиленная гидроплита dsg7; усиленная плита dsg7 dq200; усиленная гидроплита dq200; усиленная плита гидроблока; усиленная плита dsg7; гидроплита dsg7 купить; замена гидроплиты dsg7. Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и другие. Устанавливается в штатное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat с коробкой DSG DQ200 0AM/0CW. Подходит для СТО и самостоятельного ремонта.
-В наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW.
-Установка данной плиты устраняет проблему с давлением в мехатронике 0AM325025 (ошибки P17BF и др.).
-Усиление стенки увеличивает ресурс мехатроника DQ200 (оригинальная плита с тонкой стенкой часто лопается).
-Сотрудничаем с заводом несколько лет.
-Отличное качество гидроплиты DQ200.
-Наша плита DSG7 не лопается и держит давление!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1801,27 +1662,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
+          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Шток сцепления DSG7 DQ200 0AM325091E — длинный, 101 мм
-Оригинальный длинный шток (0AM325091E) для мехатроника DSG7 DQ200 0AM / 0CW. Используется в коробках dq200 старого типа (до 2012 года). Обеспечивает точную передачу усилия к муфте сцепления.
-Подходит для:
-• DSG7 DQ200 (сухое 7-ступенчатое сцепление)
-• VW, Audi, Skoda, Seat 2012–2025
-• Артикул: 0AM325091E — длинный шток 101 мм
-Когда менять:
-• При износе, деформации или нарушении передачи усилия
-• После 90 000–100 000 км или при ремонте сцепления
-• Рекомендуется менять вместе с сальниками и пыльником
-Преимущества:
-• Проверенный поставщик
-• Отличное качество, каждый шток проходит проверку
-Очень быстрая отправка
-Установите правильный новый шток — никаких лишних поездок в автосервис.
-Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; шток дсг 7; шток сцепления dsg 7; 0am325091e; длинный шток dsg7; 101 мм шток dsg7; шток мехатроника 101 мм; замена штоков мехатроника dsg 7; установка штока dsg7; купить шток dsg7; штоки сцепления dsg; шток dsg 7 нового образца.</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1840,26 +1686,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG 7 DQ200 0am325091f 99 мм короткий 1шт</t>
+          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Шток сцепления DSG7 DQ200 0AM325091F — короткий, 99 мм
-Оригинальный шток сцепления (0AM325091F) для DSG7 DQ200 — короткий вариант на 99 мм. Используется в коробках передач до 2012 года (старого образца). Отвечает за точную работу механизма сцепления.
-Подходит для:
-• DSG7 DQ200 (7-ступ., сухая сцепа)
-• VW, Audi, Skoda, Seat (выпуск до 2012 г.)
-• Только артикул: 0AM325091F (короткий)
-Когда менять:
-• При люфте, износе, коррозии или следах масла
-• При ремонте гидроблока или полной ревизии мехатроника
-Преимущества:
-• Актуальная длина — 99 мм
-• Стабильная работа сцепления
-Очень быстрая отправка
-Проверьте длину штока и делайте заказ!
-Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; пыльник штока мехатроника dq200; шток дсг 7; штоки мехатроника дсг 7; шток сцепления дсг 7; 0am325091f; замена штоков мехатроника dsg 7 dq200; установка мехатроника dsg 7 выставление штоков; штоки сцепления dsg; штоки сцепления dsg 7; штоки dsg 7 99 и 101; замена штоков мехатроника dsg 7; ремкомплект штоков мехатроника dsg 7; короткий шток dsg7; купить шток dsg7</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1878,12 +1710,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1902,19 +1734,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
-Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
-Набор защитных пыльников (чехлов) для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобилей Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений и продлевает срок службы коробки передач.
-Используется в мехатронике DSG 7 DQ200 0AM 0CW
-Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода
-Пыльник мехатроника DSG 7 всегда в наличии
-Отличное качество
-Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходников и подвержен большому износу</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1933,36 +1758,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
-Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
-Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.
-Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.
-Применение и совместимость
-Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):
-Volkswagen
-Audi
-Skoda
-Seat
-Устанавливается в мехатроник трансмиссий с сухим сцеплением.
-Преимущества оригинальной детали Volkswagen
-Оригинальное производство Volkswagen AG (Германия)
-Точное соответствие заводским размерам
-Надёжная защита штока мехатроника
-Устойчивость к маслу, температуре и износу
-Предотвращает утечку масла и загрязнение сцепления
-Рекомендован для профессионального ремонта DSG
-Когда требуется замена пыльника
-Обнаружена утечка масла из мехатроника
-Ремонт или замена штока сцепления DSG7
-Ошибки по мехатронику DQ200
-Рывки, вибрации, нестабильная работа коробки
-Профилактика при разборке узла
-шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1981,21 +1782,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка 123014-AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG-7 (DL501 / 0B5 / DQ500 / 0BH). Используется для тонкой фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими моделями с коробками DSG-7. Лёгкая установка, полный аналог оригинала 0B5 325 421. Отличный вариант для быстрого и недорогого восстановления работоспособности АКПП. Неоригинал высокого качества.
-Подходит для:
-• DSG-7 (DL501 / 0B5 / 0BH)
-• Устанавливается в соленоиды N436 и N440
-• Аналог оригинала 0B5 325 421
-• Обеспечивает тонкую фильтрацию масла
-• Продлевает срок службы гидроблока
-• Качественная фильтр-сетка 123014-AF
-• Идеальное решение для профилактики выхода из строя соленоидов: предотвращает засорение и продлевает ресурс КПП DQ500 / 0BH
-Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501. Новая.</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2014,30 +1806,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E Новое поколение Nissan Mitsubishi Renault</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Новое поколение) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
-Описание товара
-Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.
-Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.
-Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.
-Когда требуется замена гидроблока
-• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим
-Преимущества
-• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП
-Совместимость
-Тип КПП: вариатор CVT Модель: JF011E / RE0F10A
-Применяется в автомобилях:
-Nissan
-Mitsubishi
-Renault
-Jeep
-(модели с установленным вариатором JF011E — по каталогу производителя)
-Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый
-гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2103,41 +1877,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый
-Краткое описание (первые 3 строки — самое важное для Ozon)
-Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.
-Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.
-Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.
-Признаки неисправности гидроблока JF015E:
-рывки и пинки при разгоне
-задержка включения Drive / Reverse
-пробуксовка вариатора
-переход в аварийный режим
-ошибки по давлению масла и соленоидам
-вибрации и нестабильная работа CVT
-Преимущества:
-Полная совместимость с вариатором JF015E (RE0F11A)
-Восстанавливает корректное давление масла
-Улучшает плавность хода и отклик трансмиссии
-Оптимальное решение без замены всего вариатора
-Подходит для СТО и самостоятельного ремонта
-Совместимость:
-Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)
-Часто устанавливается на:
-Nissan Juke
-Nissan Qashqai
-Nissan Note
-Nissan Sentra
-Renault Fluence
-Renault Kaptur
-Mitsubishi ASX (и другие модели с вариатором JF015E)
-Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
-гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2156,30 +1901,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
-Описание товара
-Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.
-Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.
-Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.
-Основные признаки износа гидроблока:
-• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT
-Преимущества
-• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора
-Совместимость
-Тип КПП: вариатор CVT Модель: JF015E / RE0F11A
-Подходит для автомобилей:
-Nissan
-Renault
-Mitsubishi
-(модели с установленным вариатором JF015E — по каталогу)
-Техническая информация
-Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый 
-гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2198,12 +1925,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 / 5636119</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet&lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии&lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2298,12 +2025,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2322,7 +2049,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E/RE0F10A вариатора CVT, 4 шт NSK</t>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка DSG7 DQ200</t>
+          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды DSG7 DQ200 VAG</t>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$F$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,9 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +472,16 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Цена WB, ₽ (финальная, покупателю — при пересборке подставляется текущая цена с WB)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Скидка WB, % (справочно — текущая; не редактируется отсюда, см. push_wb_price)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Заметки</t>
         </is>
       </c>
@@ -482,12 +494,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -496,7 +508,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -506,12 +524,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Корпус фильтра DQ250 DSG6 02E305045 Новый улучшает теплоотвод отличное качество - проверенный!</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -520,7 +538,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -530,12 +554,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Фильтр мехатроника DQ250 02E DSG6</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -544,7 +568,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -554,17 +584,34 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Улучшенный отвод тепла
+Уменьшает температуру масла КПП
+Резиновое кольцо в комплекте
+Алюминиевый корпус фильтра DSG6 DQ250 (02E305045)
+Надёжная замена OEM-пластика — предотвращает перегрев, трещины корпуса и продлевает срок службы DSG6.
+Артикул: 02E305045
+Совместимость: DSG6 02E (DQ250, мокрое сцепление), VW/Audi/Skoda/Seat (2004–2019)
+Преимущества:
+• Прочный алюминиевый корпус
+• Уплотнительное кольцо в комплекте
+Очень быстрая отправка
+Обновите корпус и убережёте DSG от перегрева</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -574,12 +621,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -588,7 +635,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>975</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -598,12 +651,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1шт!</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -612,7 +665,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>8244.5</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -651,7 +710,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -661,12 +726,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -675,7 +740,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -685,12 +756,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW — артикул 0AM325219C
+Крышка поддона мехатроника. Устанавливается при обслуживании DSG7 (тип DQ200). Обеспечивает герметичность и защиту внутренних элементов.
+Назначение: крышка поддона мехатроника
+Совместимость: DSG7 DQ200, мехатроники 0AM / 0CW
+Артикул: 0AM325219C
+Преимущества:
+• Подходит для плановой замены
+• Простая установка без доработок
+• Надёжная защита от пыли и масла
+Очень быстрая отправка
+Возьмите сейчас — пригодится при обслуживании или замене поддона</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -699,7 +780,13 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -709,12 +796,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -723,7 +810,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -733,12 +826,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Новый фильтр dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Для чего нужен? Для ремонта мехатроника dsg 7 dq200 0am325025 0cw</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -747,7 +840,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -757,12 +856,13 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 (артикул 0AM325443D) предназначена для герметичного соединения корпуса мехатроника на роботизированной коробке передач DSG 7 DQ 200 с  модификациями 0AM и 0CW. Усиленная прокладка используется при замене гидроблока, ревизии блока управления или устранении течи трансмиссионной жидкости.&lt;br/&gt;&lt;br/&gt;Подходит для большинства автомобилей VAG-группы (Volkswagen, Audi, Skoda, Seat), оснащённых трансмиссией DQ200. Обеспечивает надёжную герметизацию, изготовлена из термостойкого эластомера, рассчитанного на высокие нагрузки и температурные циклы.&lt;br/&gt;&lt;br/&gt;Прокладка 0AM325443D — один из ключевых элементов при ремонте мехатроника DSG 7.  Может поставляться как отдельно, так и в составе ремонтных комплектов.&lt;br/&gt;&lt;br/&gt;Прокладка для крышки мехатроника DSG7 DQ200 (0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Если у вас DQ200 то подойдет 100%. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.
+Значительно толще штатной и ходит намного дольше, заказывайте!</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -771,7 +871,13 @@
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -781,12 +887,14 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина VAG DSG7 DQ200 0AM325467J</t>
+          <t>Оригинал VAG cепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
+          <t>Оригинальная сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J
+Отличное качество VAG
+Не гнутая, ходит намного дольше аналогов, заказывайте оригинал VAG!</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -795,7 +903,13 @@
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -805,12 +919,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Соленоиды DQ200 Hilti Контрактные проверенные на стенде&lt;br/&gt;&lt;br/&gt;Минимальный пробег оригинальных соленоидов DSG7 + проверка на стенде позволяют надежно решить проблему с вышедшеми из строя соленоидами 0am 0cw.&lt;br/&gt;&lt;br/&gt;Цена указана за 4 шт - 1 половинка как на фото (1 соленоид регулятор давления + 3 Shift Шифт соленоида) контрактные б/у минимальный пробег + каждый соленоид проверяется на стенде!&lt;br/&gt;&lt;br/&gt;Всего в мехатронике устанавливаются 8 шт - 2 половинки (2 соленоида регулятора давления + 6 соленоидов Shift Шифт)&lt;br/&gt;&lt;br/&gt;Внимание - соленоиды DQ 200 качественные проверенные на стенде, если вам нужно менять полный комплект соленоидов мехатроника 0AM 8 шт - заказывайте 2 половинки по 4 шт у нас. Соленоиды Hilti как на фото - ЕСЛИ У ВАС СТОЯТ СОЛЕНОИДЫ BOSCH (с коричневым соленоидом регулятором давления) МЕНЯТЬ НУЖНО КОМПЛЕКТ ЦЕЛИКОМ - 8 БОШ на 8 БОШ, либо 8 ХИЛТИ (как у нас) на 8 ХИЛТИ. Либо если у вас стоят ХИЛТИ и вы хотите поменять 4 шт на 4 шт - так тоже можно. Не нужно ставить 4 БОШ и 4 ХИЛТИ!</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -819,7 +933,13 @@
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>8784.299999999999</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -829,12 +949,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60бар).  Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CW Volkswagen, Audi, Skoda, Seat (2007–2023 и далее) Артикул: 0AM325587E Признаки износа/неисправности: Рывки при трогании с места Долгое задержание передач D/R Код ошибки (например, P0841) Появление металлической стружки в масле Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 Преимущества замены: Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока Отправка — максимально быстро Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -843,7 +963,13 @@
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>9743.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -853,12 +979,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -867,7 +993,13 @@
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -877,17 +1009,37 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
+Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Усиленная конструкция является надежной альтернативой пластиковому корпусу, рассчитана на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и их модификациях.
+Преимущества
+• Улучшенный отвод тепла — снижает рабочую температуру масла в КПП
+• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур
+• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек
+• Многократное использование при регламентном обслуживании
+• Оптимизированная форма с ребрами для повышения эффективности охлаждения
+Совместимость
+• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
+• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
+• Seat, Skoda с коробкой DQ500 (по каталогу)
+Номер детали
+0BH325183B
+Надёжная и долговечная деталь для вашей DSG7. Быстрая отправка.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -897,17 +1049,35 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
+Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надежную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Анодированное красное покрытие дополнительно защищает металл от коррозии.
+Совместимость:
+• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
+• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
+• Seat, Skoda с коробкой DQ500 (по каталогу)
+Номер детали: 0BH325183B
+Особенности:
+• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам
+• Анодированное красное покрытие — защита от окисления и привлекательный внешний вид
+• Полная совместимость с оригинальными уплотнительными элементами
+• Повторно используемая конструкция
+Максимально быстрая отправка.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -942,7 +1112,13 @@
       </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -983,7 +1159,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="n">
+        <v>2732.24</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1025,7 +1207,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>15032.1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1035,12 +1223,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM325025</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 Плита сальники прокладки</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 включает всё необходимое для ремонта и восстановления блока управления коробки передач. В комплект входят прокладка мехатроника DQ200, сальники, уплотнения, плита мехатроника и гидроплита. Совместим с трансмиссиями DSG 7 DQ200 0am и 0cw. Используется при замене гидроплиты, ремонте блока мехатроника (замене прокладок) или полной ревизии DSG. Ремкомплект подходит для большинства моделей VAG-группы (Volkswagen, Audi, Skoda, Seat) с коробкой DQ200. Детали высокого качества, проверенные временем. Прокладка крышки, комплект прокладок DSG 7, ремкомплект мехатроника купить — всё это вы найдёте в данном наборе.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1049,7 +1237,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1059,12 +1253,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1073,7 +1267,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1083,12 +1283,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльники крышки</t>
+          <t>Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальника 2 крышки</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1097,7 +1297,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1140,7 +1346,13 @@
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>9743.5</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1150,12 +1362,43 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769D</t>
+          <t>Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Каждый мехатроник DSG7 DQ200 проходит полную проверку на автомобиле после сборки.
+Мы не ограничиваемся стендовыми тестами — каждый мехатроник обязательно проходит обкатку на дороге, в реальных условиях эксплуатации. 
+ • Каждый соленоид — оригинальный, проходит проверку на стенде
+ • Тестирование выполняется с сопоставлением графиков с эталонными значениями, загруженными в систему
+ • Любое отклонение — соленоид отбраковывается
+Используем
+Оригинальные запчасти VAG:
+ • Крышка мехатроника
+ • Сепараторная пластина под гидроплиту 0AM
+ • Пластины соленоидов
+ • Втулки штоков мехатроника DSG7 DQ200
+Усовершенствованные компоненты:
+ • Усиленная прокладка крышки мехатроника (утолщенная, увеличенный ресурс)
+ • Алюминиевые сальники толкателей вилок (высокое качество, не пластик и не дешевые аналоги)
+ • Усиленные штоки DQ200 с дополнительной резинкой (повышенный срок службы)
+ • Стальная вставка высокого качества+комплект надежных уплотнений (не теряют давление со временем)
+ • Качественный ремкомплект прокладок мехатроника DSG7 DQ200
+Электронная часть:
+ • Устанавливается качественная электронная плата 0AM927769D
+ • Многолетний опыт производства и тестирования электронных компонентов
+Финальные испытания:
+ • Каждый мехатроник проверяется на мини-стенде под давлением
+ • Контроль времени сброса давления
+ • Проверка работы толкателей и герметичности системы
+Главное преимущество — проверка на автомобиле:
+В отличие от большинства сервисов (99%), где мехатроник просто собирается и отдается клиенту, мы выполняем полноценную проверку DSG7 DQ200 в движении.
+Проверка на дороге — это:
+ • работа всех систем под нагрузкой
+ • реальное переключение передач
+ • полноценная диагностика агрегата в сборе
+Только такой подход позволяет гарантировать, что мехатроник действительно исправен, а не «условно рабочий».
+Заказывайте восстановленные мехатроники DSG7 DQ200, полностью протестированные на авто, с оригинальными и улучшенными компонентами — по выгодной цене и с реальной гарантией работы.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1164,7 +1407,13 @@
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>113525</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1174,12 +1423,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1188,7 +1437,13 @@
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1232,7 +1487,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="n">
+        <v>85025</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1242,12 +1503,21 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Крышка мехатроника DSG7 + прокладка поддона dq200 набор</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t xml:space="preserve">ОРИГИНАЛ VAG Крышка мехатроника DSG7 DQ200 (0AM325219C) + усиленная прокладка с утолщением мехатроника DQ200 DSG7(0AM325443D)
+Комплект для восстановления герметичности масляной крышки (поддона) при обслуживании мехатроника DSG7. Подходит для 7-ступенчатой коробки с сухим сцеплением (DQ200 всех модификаций).
+Артикулы: 0AM325219C + 0AM325443D
+Совместимость: DSG7 (DQ200, 7-ступ., сухое сцепление), 0AM / 0CW, VW/Audi/Skoda/Seat
+Преимущества:
+• Точный OEM-аналог без доработок
+• Устойчив к давлению и нагреву
+Очень быстрая отправка
+Набор пригодится при плановом обслуживании или замене крышки (поддона)
+Самый эффективный и качественный вариант - оригинал VAG + усовершенствованная прокладка - лучшее и самое надежное решение </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1256,7 +1526,13 @@
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n">
+        <v>3920</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1266,12 +1542,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7 шт.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1280,7 +1556,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1290,12 +1572,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
+          <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
+Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
+Все необходимые прокладки в ремкомплекте:
+Прокладка поддона
+Фильтр мехатроника 0AM325433E, 0AM325433B
+Пыльники штоков сцепления DSG7 DQ200 0AM, 0CW, 0AM325091F, 0AM325091E
+И так далее.
+Покупая наш ремонтный комплект гидроблока DSG7 0AM/0CW, вы выполняете полноценный ремонт мехатроника, меняя все расходники и устанавливая новую усиленную гидроплиту 0AM325066AE.
+Ошибки: P17BF, P189C, P0841, P1895
+Артикулы: 0AM325025D; 0AM325025DX; 0AM325025H; 0AM325025HX; 0AM325025L; 0AM325025LX; 0AM325025M; 0AM325025MX; 0AM325025K; 0AM325025N; 0AM325025R; 0AM325026A; 0AM325026C; 0AM325025DZSN; 0AM325025DZEM.
+Заказывайте!</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1304,7 +1596,13 @@
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>4160</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1314,12 +1612,16 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Оригинал VAG пластины мехатроиника dsg7 dq200</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7 + пластины на соленоиды dsg7 
+Новые ОРИГИНАЛ VAG
+Напрямую с завода
+Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)
+Оригинал Volkswagen отличное качество, ходят намного дольше, не гнутые, заказывайте!</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1328,7 +1630,13 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1338,12 +1646,15 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
+          <t>Усиленный Новый поршень штока мехатроника DQ200 DSG 7 0AM 0CW
+Отличное качество - за счет усовершенствованной конструкции (доп резинки) ходит намного дольше
+Подходит на все штоки 0am325091E (101мм длинный) 0am325091F (99мм короткий)
+Продлите работу штоков и всего мехатроника в целом, заказывайте!</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1352,7 +1663,13 @@
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1362,12 +1679,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1376,7 +1693,13 @@
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="n">
+        <v>8443.5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1386,12 +1709,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
+          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1400,7 +1723,13 @@
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n">
+        <v>8378.5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1410,12 +1739,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1424,7 +1753,13 @@
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1434,12 +1769,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1448,7 +1783,13 @@
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="n">
+        <v>1475</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1458,12 +1799,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект длинный шток 101мм 0AM325091E + DSG7 DQ200</t>
+          <t>Длинный шток 0AM325091E 101 мм+втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1472,7 +1813,13 @@
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1482,12 +1829,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 99мм 0AM325091F + DSG7 DQ200</t>
+          <t>Короткий шток 0AM325091F 99 мм+втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка
+Комплект: короткий шток сцепления 0AM325091F (99 мм) и гильза мехатроника DSG7 DQ200. Устраняет люфт и обеспечивает точную и надёжную работу сцепления.
+Совместимость:
+• DSG7 DQ200 (7-ступ., сухое сцепление)
+• VW / Audi / Skoda / Seat (до 2012 года)
+• Артикул штока: 0AM325091F
+Когда нужен:
+• Люфт или износ штока или втулки (гильзы)
+• Ошибки сцепления или гидроблока
+• Профилактика или ремонт мехатроника
+Особенности:
+• Шток 99 мм — точный заводской размер
+• Новая втулка — без повреждений
+• Отличное качество материалов
+Очень быстрая отправка
+Восстановите мехатроник сразу с ремкомплектом и без лишних затрат.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1496,7 +1858,13 @@
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1556,7 +1924,13 @@
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
+        <v>69302.22</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1566,12 +1940,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1580,7 +1954,13 @@
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1590,12 +1970,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1604,7 +1984,13 @@
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1614,12 +2000,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
+          <t>Сальник манжет штока сцепления мехатроник DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1628,7 +2014,13 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1638,12 +2030,29 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+          <t>Усиленная гидроплита DSG7 DQ200 — 0AM325066AE / 0CW
+Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW) с увеличенной толщиной стенки. Обеспечивает стабильность давления и предотвращает ошибки P17BF/P1895 и другие при интенсивной эксплуатации.
+Совместимость:
+• DSG7 DQ200 (7-ступ., сухое сцепление)
+• VW, Audi, Skoda, Seat (2007–2025)
+• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C и другие. Устанавливается на мехатроники 0AM325025H и другие варианты, а также на мехатроники 0CW.
+Особенности:
+• Увеличенная толщина стенки в зоне гидроаккумулятора
+• Хорошее качество алюминия
+Очень быстрая отправка
+Решение для тех, кто хочет надёжность без риска ошибок и поломок DSG7.
+В описании использованы запросы: плита дсг; гидроплита dsg; гидроплита мехатроника; гидроплита дсг 7; плита dq200; гидроплита dq200; плита мехатроника dsg; гидроплита dsg 7 dq200; момент затяжки гидроплиты; усиленная плита мехатроника dq200; 0am325066ae; усиленная гидроплита dsg7; усиленная плита dsg7 dq200; усиленная гидроплита dq200; усиленная плита гидроблока; усиленная плита dsg7; гидроплита dsg7 купить; замена гидроплиты dsg7. Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и другие. Устанавливается в штатное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat с коробкой DSG DQ200 0AM/0CW. Подходит для СТО и самостоятельного ремонта.
+В наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW.
+Установка данной плиты устраняет проблему с давлением в мехатронике 0AM325025 (ошибки P17BF и др.).
+Усиление стенки увеличивает ресурс мехатроника DQ200 (оригинальная плита с тонкой стенкой часто лопается).
+Сотрудничаем с заводом несколько лет.
+Отличное качество гидроплиты DQ200.
+Наша плита DSG7 не лопается и держит давление!</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1652,7 +2061,13 @@
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
+        <v>7347.3</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1662,12 +2077,27 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Шток сцепления DSG7 DQ200 0AM325091E — длинный, 101 мм
+Оригинальный длинный шток (0AM325091E) для мехатроника DSG7 DQ200 0AM / 0CW. Используется в коробках dq200 старого типа (до 2012 года). Обеспечивает точную передачу усилия к муфте сцепления.
+Подходит для:
+• DSG7 DQ200 (сухое 7-ступенчатое сцепление)
+• VW, Audi, Skoda, Seat 2012–2025
+• Артикул: 0AM325091E — длинный шток 101 мм
+Когда менять:
+• При износе, деформации или нарушении передачи усилия
+• После 90 000–100 000 км или при ремонте сцепления
+• Рекомендуется менять вместе с сальниками и пыльником
+Преимущества:
+• Проверенный поставщик
+• Отличное качество, каждый шток проходит проверку
+Очень быстрая отправка
+Установите правильный новый шток — никаких лишних поездок в автосервис.
+Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; шток дсг 7; шток сцепления dsg 7; 0am325091e; длинный шток dsg7; 101 мм шток dsg7; шток мехатроника 101 мм; замена штоков мехатроника dsg 7; установка штока dsg7; купить шток dsg7; штоки сцепления dsg; шток dsg 7 нового образца.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1676,7 +2106,13 @@
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1686,12 +2122,26 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Шток мехатроника DSG 7 DQ200 0am325091f 99 мм короткий 1шт</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Шток сцепления DSG7 DQ200 0AM325091F — короткий, 99 мм
+Оригинальный шток сцепления (0AM325091F) для DSG7 DQ200 — короткий вариант на 99 мм. Используется в коробках передач до 2012 года (старого образца). Отвечает за точную работу механизма сцепления.
+Подходит для:
+• DSG7 DQ200 (7-ступ., сухая сцепа)
+• VW, Audi, Skoda, Seat (выпуск до 2012 г.)
+• Только артикул: 0AM325091F (короткий)
+Когда менять:
+• При люфте, износе, коррозии или следах масла
+• При ремонте гидроблока или полной ревизии мехатроника
+Преимущества:
+• Актуальная длина — 99 мм
+• Стабильная работа сцепления
+Очень быстрая отправка
+Проверьте длину штока и делайте заказ!
+Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; пыльник штока мехатроника dq200; шток дсг 7; штоки мехатроника дсг 7; шток сцепления дсг 7; 0am325091f; замена штоков мехатроника dsg 7 dq200; установка мехатроника dsg 7 выставление штоков; штоки сцепления dsg; штоки сцепления dsg 7; штоки dsg 7 99 и 101; замена штоков мехатроника dsg 7; ремкомплект штоков мехатроника dsg 7; короткий шток dsg7; купить шток dsg7</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1700,7 +2150,13 @@
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1710,12 +2166,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1724,7 +2180,13 @@
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="n">
+        <v>2447.15</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1734,12 +2196,19 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
+Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
+Набор защитных пыльников (чехлов) для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобилей Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений и продлевает срок службы коробки передач.
+Используется в мехатронике DSG 7 DQ200 0AM 0CW
+Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода
+Пыльник мехатроника DSG 7 всегда в наличии
+Отличное качество
+Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходников и подвержен большому износу</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1748,7 +2217,13 @@
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1758,12 +2233,36 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
+          <t>Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
+Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
+Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.
+Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.
+Применение и совместимость
+Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):
+Volkswagen
+Audi
+Skoda
+Seat
+Устанавливается в мехатроник трансмиссий с сухим сцеплением.
+Преимущества оригинальной детали Volkswagen
+Оригинальное производство Volkswagen AG (Германия)
+Точное соответствие заводским размерам
+Надёжная защита штока мехатроника
+Устойчивость к маслу, температуре и износу
+Предотвращает утечку масла и загрязнение сцепления
+Рекомендован для профессионального ремонта DSG
+Когда требуется замена пыльника
+Обнаружена утечка масла из мехатроника
+Ремонт или замена штока сцепления DSG7
+Ошибки по мехатронику DQ200
+Рывки, вибрации, нестабильная работа коробки
+Профилактика при разборке узла
+шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1772,7 +2271,13 @@
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1782,12 +2287,21 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
+          <t>Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Фильтр-сетка 123014-AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG-7 (DL501 / 0B5 / DQ500 / 0BH). Используется для тонкой фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими моделями с коробками DSG-7. Лёгкая установка, полный аналог оригинала 0B5 325 421. Отличный вариант для быстрого и недорогого восстановления работоспособности АКПП. Неоригинал высокого качества.
+Подходит для:
+• DSG-7 (DL501 / 0B5 / 0BH)
+• Устанавливается в соленоиды N436 и N440
+• Аналог оригинала 0B5 325 421
+• Обеспечивает тонкую фильтрацию масла
+• Продлевает срок службы гидроблока
+• Качественная фильтр-сетка 123014-AF
+• Идеальное решение для профилактики выхода из строя соленоидов: предотвращает засорение и продлевает ресурс КПП DQ500 / 0BH
+Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501. Новая.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1796,7 +2310,13 @@
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1806,12 +2326,30 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Гидроблок JF011E Новое поколение Nissan Mitsubishi Renault</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
+          <t>Гидроблок JF011E (Новое поколение) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
+Описание товара
+Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.
+Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.
+Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.
+Когда требуется замена гидроблока
+• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим
+Преимущества
+• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП
+Совместимость
+Тип КПП: вариатор CVT Модель: JF011E / RE0F10A
+Применяется в автомобилях:
+Nissan
+Mitsubishi
+Renault
+Jeep
+(модели с установленным вариатором JF011E — по каталогу производителя)
+Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый
+гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1820,7 +2358,13 @@
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1867,7 +2411,13 @@
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1877,12 +2427,41 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mitsubishi</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый
+Краткое описание (первые 3 строки — самое важное для Ozon)
+Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.
+Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.
+Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.
+Признаки неисправности гидроблока JF015E:
+рывки и пинки при разгоне
+задержка включения Drive / Reverse
+пробуксовка вариатора
+переход в аварийный режим
+ошибки по давлению масла и соленоидам
+вибрации и нестабильная работа CVT
+Преимущества:
+Полная совместимость с вариатором JF015E (RE0F11A)
+Восстанавливает корректное давление масла
+Улучшает плавность хода и отклик трансмиссии
+Оптимальное решение без замены всего вариатора
+Подходит для СТО и самостоятельного ремонта
+Совместимость:
+Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)
+Часто устанавливается на:
+Nissan Juke
+Nissan Qashqai
+Nissan Note
+Nissan Sentra
+Renault Fluence
+Renault Kaptur
+Mitsubishi ASX (и другие модели с вариатором JF015E)
+Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
+гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1891,7 +2470,13 @@
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n">
+        <v>42408</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1901,12 +2486,30 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mitsubishi</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
+Описание товара
+Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.
+Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.
+Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.
+Основные признаки износа гидроблока:
+• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT
+Преимущества
+• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора
+Совместимость
+Тип КПП: вариатор CVT Модель: JF015E / RE0F11A
+Подходит для автомобилей:
+Nissan
+Renault
+Mitsubishi
+(модели с установленным вариатором JF015E — по каталогу)
+Техническая информация
+Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый 
+гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1915,7 +2518,13 @@
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="n">
+        <v>40052</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1925,12 +2534,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Импульсное кольцо распредвала GM 55565480 / 5636119</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet&lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии&lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1939,7 +2548,13 @@
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1964,7 +2579,13 @@
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1991,7 +2612,13 @@
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="n">
+        <v>1564.8</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2009,13 +2636,15 @@
           <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TESTWB001_2.jpg</t>
-        </is>
-      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2025,12 +2654,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2039,7 +2668,13 @@
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2049,7 +2684,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+          <t>Комплект подшипников JF011E/RE0F10A вариатора CVT, 4 шт NSK</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2063,10 +2698,16 @@
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F61"/>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$61</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860387/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -519,75 +519,106 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02E305045E</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG6 02E305045 Новый улучшает теплоотвод отличное качество - проверенный!</t>
+          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
+Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://basket-38.wbbasket.ru/vol8361/part836194/836194897/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>02E305045E</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+          <t>Корпус фильтра DQ250 DSG6 02E305045 Новый улучшает теплоотвод отличное качество - проверенный!</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670858/670858041/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670858/670858041/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670858/670858041/images/big/3.webp</t>
+          <t>https://basket-38.wbbasket.ru/vol8361/part836194/836194897/images/big/1.webp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>1770</v>
+        <v>1710</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>02E305051C</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>02e305045</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DSG6 DQ250 02E305045</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -603,88 +634,92 @@
 Обновите корпус и убережёте DSG от перегрева</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>0AM301212A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670854/670854126/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>975</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1шт!</t>
+          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925505/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>8244.5</v>
+        <v>975</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>0AM325025B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1шт!</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>8244.5</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>0AM325091E / 0AM325091F</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Сальник штока DSG7 DQ200 0AM 0CW оригинал Volkswagen</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -704,62 +739,62 @@
 Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7114/part711488/711488868/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="n">
-        <v>1319.7</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>0AM325120A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670869/670869831/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670869/670869831/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670869/670869831/images/big/3.webp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>675</v>
+        <v>1319.7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>0AM325120A</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>0AM325219C</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW — артикул 0AM325219C
 Крышка поддона мехатроника. Устанавливается при обслуживании DSG7 (тип DQ200). Обеспечивает герметичность и защиту внутренних элементов.
@@ -774,245 +809,245 @@
 Возьмите сейчас — пригодится при обслуживании или замене поддона</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925525/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="n">
-        <v>2475</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>0AM325413A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
-        </is>
-      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862903/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>675</v>
+        <v>2475</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Новый фильтр dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Для чего нужен? Для ремонта мехатроника dsg 7 dq200 0am325025 0cw</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670855/670855815/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670855/670855815/images/big/2.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>1250</v>
+        <v>675</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Новый фильтр dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Для чего нужен? Для ремонта мехатроника dsg 7 dq200 0am325025 0cw</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>0AM325443D</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 (артикул 0AM325443D) предназначена для герметичного соединения корпуса мехатроника на роботизированной коробке передач DSG 7 DQ 200 с  модификациями 0AM и 0CW. Усиленная прокладка используется при замене гидроблока, ревизии блока управления или устранении течи трансмиссионной жидкости.&lt;br/&gt;&lt;br/&gt;Подходит для большинства автомобилей VAG-группы (Volkswagen, Audi, Skoda, Seat), оснащённых трансмиссией DQ200. Обеспечивает надёжную герметизацию, изготовлена из термостойкого эластомера, рассчитанного на высокие нагрузки и температурные циклы.&lt;br/&gt;&lt;br/&gt;Прокладка 0AM325443D — один из ключевых элементов при ремонте мехатроника DSG 7.  Может поставляться как отдельно, так и в составе ремонтных комплектов.&lt;br/&gt;&lt;br/&gt;Прокладка для крышки мехатроника DSG7 DQ200 (0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Если у вас DQ200 то подойдет 100%. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.
 Значительно толще штатной и ходит намного дольше, заказывайте!</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860106/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860106/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860106/images/big/3.webp</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="n">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
         <v>1470</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>0AM325467J</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Оригинал VAG cепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Оригинальная сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J
 Отличное качество VAG
 Не гнутая, ходит намного дольше аналогов, заказывайте оригинал VAG!</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670854/670854239/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Соленоиды DQ200 Hilti Контрактные проверенные на стенде&lt;br/&gt;&lt;br/&gt;Минимальный пробег оригинальных соленоидов DSG7 + проверка на стенде позволяют надежно решить проблему с вышедшеми из строя соленоидами 0am 0cw.&lt;br/&gt;&lt;br/&gt;Цена указана за 4 шт - 1 половинка как на фото (1 соленоид регулятор давления + 3 Shift Шифт соленоида) контрактные б/у минимальный пробег + каждый соленоид проверяется на стенде!&lt;br/&gt;&lt;br/&gt;Всего в мехатронике устанавливаются 8 шт - 2 половинки (2 соленоида регулятора давления + 6 соленоидов Shift Шифт)&lt;br/&gt;&lt;br/&gt;Внимание - соленоиды DQ 200 качественные проверенные на стенде, если вам нужно менять полный комплект соленоидов мехатроника 0AM 8 шт - заказывайте 2 половинки по 4 шт у нас. Соленоиды Hilti как на фото - ЕСЛИ У ВАС СТОЯТ СОЛЕНОИДЫ BOSCH (с коричневым соленоидом регулятором давления) МЕНЯТЬ НУЖНО КОМПЛЕКТ ЦЕЛИКОМ - 8 БОШ на 8 БОШ, либо 8 ХИЛТИ (как у нас) на 8 ХИЛТИ. Либо если у вас стоят ХИЛТИ и вы хотите поменять 4 шт на 4 шт - так тоже можно. Не нужно ставить 4 БОШ и 4 ХИЛТИ!</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670869/670869819/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>8784.299999999999</v>
+        <v>1400</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60бар).  Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CW Volkswagen, Audi, Skoda, Seat (2007–2023 и далее) Артикул: 0AM325587E Признаки износа/неисправности: Рывки при трогании с места Долгое задержание передач D/R Код ошибки (например, P0841) Появление металлической стружки в масле Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 Преимущества замены: Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока Отправка — максимально быстро Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>Соленоиды DQ200 Hilti Контрактные проверенные на стенде&lt;br/&gt;&lt;br/&gt;Минимальный пробег оригинальных соленоидов DSG7 + проверка на стенде позволяют надежно решить проблему с вышедшеми из строя соленоидами 0am 0cw.&lt;br/&gt;&lt;br/&gt;Цена указана за 4 шт - 1 половинка как на фото (1 соленоид регулятор давления + 3 Shift Шифт соленоида) контрактные б/у минимальный пробег + каждый соленоид проверяется на стенде!&lt;br/&gt;&lt;br/&gt;Всего в мехатронике устанавливаются 8 шт - 2 половинки (2 соленоида регулятора давления + 6 соленоидов Shift Шифт)&lt;br/&gt;&lt;br/&gt;Внимание - соленоиды DQ 200 качественные проверенные на стенде, если вам нужно менять полный комплект соленоидов мехатроника 0AM 8 шт - заказывайте 2 половинки по 4 шт у нас. Соленоиды Hilti как на фото - ЕСЛИ У ВАС СТОЯТ СОЛЕНОИДЫ BOSCH (с коричневым соленоидом регулятором давления) МЕНЯТЬ НУЖНО КОМПЛЕКТ ЦЕЛИКОМ - 8 БОШ на 8 БОШ, либо 8 ХИЛТИ (как у нас) на 8 ХИЛТИ. Либо если у вас стоят ХИЛТИ и вы хотите поменять 4 шт на 4 шт - так тоже можно. Не нужно ставить 4 БОШ и 4 ХИЛТИ!</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670911/670911962/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>9743.5</v>
+        <v>8784.299999999999</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60бар).  Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CW Volkswagen, Audi, Skoda, Seat (2007–2023 и далее) Артикул: 0AM325587E Признаки износа/неисправности: Рывки при трогании с места Долгое задержание передач D/R Код ошибки (например, P0841) Появление металлической стружки в масле Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 Преимущества замены: Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока Отправка — максимально быстро Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860344/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860344/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860344/images/big/3.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>2475</v>
+        <v>9743.5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>0AM927769D</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>0BH325183</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Усиленная конструкция является надежной альтернативой пластиковому корпусу, рассчитана на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и их модификациях.
@@ -1031,28 +1066,32 @@
 Надёжная и долговечная деталь для вашей DSG7. Быстрая отправка.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="n">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>0BH325183 B</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надежную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Анодированное красное покрытие дополнительно защищает металл от коррозии.
@@ -1069,28 +1108,32 @@
 Максимально быстрая отправка.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="n">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Алюминиевый корпус фильтра DSG7 DQ500 — 0BH325183B
 Надёжный алюминиевый корпус фильтра, совместимый с 7-ступенчатой коробкой передач DSG DQ500 с мокрым сцеплением. Является лучшей альтернативой пластиковому варианту — отлично справляется с охлаждением и защитой масляного фильтра.
@@ -1110,28 +1153,32 @@
 Резиновое кольцо в комплекте</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="n">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>0BH325183BB</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -1153,32 +1200,32 @@
 </t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7115/part711572/711572626/images/big/1.webp</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="n">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
         <v>2732.24</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>0am3250066AE</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроник DQ200 DSG7+оригинал пыльник сальник W</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW ОРИГИНАЛЫ РАСХОДНИКИ Volkswagen
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -1201,122 +1248,172 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7115/part711549/711549088/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="n">
-        <v>15032.1</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 Плита сальники прокладки</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 включает всё необходимое для ремонта и восстановления блока управления коробки передач. В комплект входят прокладка мехатроника DQ200, сальники, уплотнения, плита мехатроника и гидроплита. Совместим с трансмиссиями DSG 7 DQ200 0am и 0cw. Используется при замене гидроплиты, ремонте блока мехатроника (замене прокладок) или полной ревизии DSG. Ремкомплект подходит для большинства моделей VAG-группы (Volkswagen, Audi, Skoda, Seat) с коробкой DQ200. Детали высокого качества, проверенные временем. Прокладка крышки, комплект прокладок DSG 7, ремкомплект мехатроника купить — всё это вы найдёте в данном наборе.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860331/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860331/images/big/2.webp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>10800</v>
+        <v>15032.1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 Плита сальники прокладки</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 включает всё необходимое для ремонта и восстановления блока управления коробки передач. В комплект входят прокладка мехатроника DQ200, сальники, уплотнения, плита мехатроника и гидроплита. Совместим с трансмиссиями DSG 7 DQ200 0am и 0cw. Используется при замене гидроплиты, ремонте блока мехатроника (замене прокладок) или полной ревизии DSG. Ремкомплект подходит для большинства моделей VAG-группы (Volkswagen, Audi, Skoda, Seat) с коробкой DQ200. Детали высокого качества, проверенные временем. Прокладка крышки, комплект прокладок DSG 7, ремкомплект мехатроника купить — всё это вы найдёте в данном наборе.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670854/670854215/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>2650</v>
+        <v>10800</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальника 2 крышки</t>
+          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670858/670858166/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>3760</v>
+        <v>2650</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>0am325025G</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальника 2 крышки</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>0am325025H</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
+без электронной платы только гидравлика
+Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
+Для каких автомобилей подходит
+Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) 
+Audi (A1, A3, TT, Q2 и др.) 
+Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)
+Почему часто нужен ремонт / замена мехатроника DQ200
+У блока DQ200 0AM/0CW есть типичные слабые места: 
+Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
+Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
+Типичные симптомы:
+ошибки давления (P17BF, P189C/P1895, P06293 и др.) 
+грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях 
+Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — готовый к установке блок (без электронной платы только гидравлика)
+Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).
+Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.
+Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. 
+ Что входит:
+Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, штоки, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды..
+</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>85025</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>0am325025HC</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроник DSG7 DQ200+пыльник сальник Оригинал</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -1340,32 +1437,32 @@
 </t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7115/part711552/711552729/images/big/1.webp</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="n">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
         <v>9743.5</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Каждый мехатроник DSG7 DQ200 проходит полную проверку на автомобиле после сборки.
 Мы не ограничиваемся стендовыми тестами — каждый мехатроник обязательно проходит обкатку на дороге, в реальных условиях эксплуатации. 
@@ -1401,94 +1498,14 @@
 Заказывайте восстановленные мехатроники DSG7 DQ200, полностью протестированные на авто, с оригинальными и улучшенными компонентами — по выгодной цене и с реальной гарантией работы.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/1.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/2.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/3.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/4.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/5.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/6.webp|https://basket-41.wbbasket.ru/vol10074/part1007465/1007465575/images/big/7.webp</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="n">
-        <v>113525</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>0am325025P</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670861/670861565/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="n">
-        <v>980</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>0am325025Y</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
-без электронной платы только гидравлика
-Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
-Для каких автомобилей подходит
-Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) 
-Audi (A1, A3, TT, Q2 и др.) 
-Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)
-Почему часто нужен ремонт / замена мехатроника DQ200
-У блока DQ200 0AM/0CW есть типичные слабые места: 
-Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
-Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
-Типичные симптомы:
-ошибки давления (P17BF, P189C/P1895, P06293 и др.) 
-грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях 
-Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — готовый к установке блок (без электронной платы только гидравлика)
-Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).
-Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.
-Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. 
- Что входит:
-Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, штоки, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды..
-</t>
-        </is>
-      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/1.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/2.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/3.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/4.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/5.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/6.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/7.webp|https://basket-33.wbbasket.ru/vol6815/part681503/681503332/images/big/8.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>85025</v>
+        <v>113525</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5</v>
@@ -1498,15 +1515,45 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>0am325025P</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>0am325025ae</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 + прокладка поддона dq200 набор</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОРИГИНАЛ VAG Крышка мехатроника DSG7 DQ200 (0AM325219C) + усиленная прокладка с утолщением мехатроника DQ200 DSG7(0AM325443D)
 Комплект для восстановления герметичности масляной крышки (поддона) при обслуживании мехатроника DSG7. Подходит для 7-ступенчатой коробки с сухим сцеплением (DQ200 всех модификаций).
@@ -1520,62 +1567,62 @@
 Самый эффективный и качественный вариант - оригинал VAG + усовершенствованная прокладка - лучшее и самое надежное решение </t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925563/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="n">
-        <v>3920</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>0am325025f</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7 шт.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
-        </is>
-      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860368/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860368/images/big/2.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>4440</v>
+        <v>3920</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>0am325025h</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7 шт.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>0am325025hfe</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
 Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
@@ -1590,32 +1637,32 @@
 Заказывайте!</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925490/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="n">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
         <v>4160</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Оригинал VAG пластины мехатроиника dsg7 dq200</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7 + пластины на соленоиды dsg7 
 Новые ОРИГИНАЛ VAG
@@ -1624,32 +1671,32 @@
 Оригинал Volkswagen отличное качество, ходят намного дольше, не гнутые, заказывайте!</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862709/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670862/670862709/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670862/670862709/images/big/3.webp</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="n">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
         <v>1950</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Усиленный Новый поршень штока мехатроника DQ200 DSG 7 0AM 0CW
 Отличное качество - за счет усовершенствованной конструкции (доп резинки) ходит намного дольше
@@ -1657,74 +1704,44 @@
 Продлите работу штоков и всего мехатроника в целом, заказывайте!</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860204/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="n">
-        <v>1325</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>0am325025m</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
-        </is>
-      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862784/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670862/670862784/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670862/670862784/images/big/3.webp|https://basket-32.wbbasket.ru/vol6708/part670862/670862784/images/big/4.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>8443.5</v>
+        <v>1325</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
+          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670854/670854144/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>8378.5</v>
+        <v>8443.5</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>35</v>
@@ -1734,105 +1751,135 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
+          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670854/670854223/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670854/670854223/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670854/670854223/images/big/3.webp|https://basket-32.wbbasket.ru/vol6708/part670854/670854223/images/big/4.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>980</v>
+        <v>8378.5</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670869/670869838/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>1475</v>
+        <v>980</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Длинный шток 0AM325091E 101 мм+втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860803/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>3430</v>
+        <v>1475</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>0am325025u</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Длинный шток 0AM325091E 101 мм+втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>0am325025z</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Короткий шток 0AM325091F 99 мм+втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка
 Комплект: короткий шток сцепления 0AM325091F (99 мм) и гильза мехатроника DSG7 DQ200. Устраняет люфт и обеспечивает точную и надёжную работу сцепления.
@@ -1852,32 +1899,32 @@
 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат.</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925480/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="n">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
         <v>3430</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>0am325025ze</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 0AM Новые соленоиды Bosch</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Абсолютно новый мехатроник DSG7 DQ200 (0AM / 0CW) — гидравлическая часть
 В продаже полностью восстановленный до состояния нового мехатроник DSG7 DQ200 для коробок передач 0AM и 0CW. Узел собран с использованием новых оригинальных и OEM-компонентов, прошёл обязательную проверку и готов к установке.
@@ -1918,122 +1965,122 @@
 Капитальном ремонте коробки DQ200</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7167/part716791/716791826/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="n">
-        <v>69302.22</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860816/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670860/670860816/images/big/2.webp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="n">
-        <v>980</v>
+        <v>69302.22</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862819/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>1325</v>
+        <v>980</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Сальник манжет штока сцепления мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670855/670855859/images/big/1.webp|https://basket-32.wbbasket.ru/vol6708/part670855/670855859/images/big/2.webp|https://basket-32.wbbasket.ru/vol6708/part670855/670855859/images/big/3.webp|https://basket-32.wbbasket.ru/vol6708/part670855/670855859/images/big/4.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>980</v>
+        <v>1325</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Сальник манжет штока сцепления мехатроник DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита DSG7 DQ200 — 0AM325066AE / 0CW
 Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW) с увеличенной толщиной стенки. Обеспечивает стабильность давления и предотвращает ошибки P17BF/P1895 и другие при интенсивной эксплуатации.
@@ -2055,32 +2102,32 @@
 Наша плита DSG7 не лопается и держит давление!</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925467/images/big/1.webp|https://basket-32.wbbasket.ru/vol6709/part670925/670925467/images/big/2.webp</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="n">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
         <v>7347.3</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Шток сцепления DSG7 DQ200 0AM325091E — длинный, 101 мм
 Оригинальный длинный шток (0AM325091E) для мехатроника DSG7 DQ200 0AM / 0CW. Используется в коробках dq200 старого типа (до 2012 года). Обеспечивает точную передачу усилия к муфте сцепления.
@@ -2100,32 +2147,32 @@
 Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; шток дсг 7; шток сцепления dsg 7; 0am325091e; длинный шток dsg7; 101 мм шток dsg7; шток мехатроника 101 мм; замена штоков мехатроника dsg 7; установка штока dsg7; купить шток dsg7; штоки сцепления dsg; шток dsg 7 нового образца.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925587/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="n">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="n">
         <v>2850</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>0am325091f</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Шток мехатроника DSG 7 DQ200 0am325091f 99 мм короткий 1шт</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Шток сцепления DSG7 DQ200 0AM325091F — короткий, 99 мм
 Оригинальный шток сцепления (0AM325091F) для DSG7 DQ200 — короткий вариант на 99 мм. Используется в коробках передач до 2012 года (старого образца). Отвечает за точную работу механизма сцепления.
@@ -2144,62 +2191,62 @@
 Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; пыльник штока мехатроника dq200; шток дсг 7; штоки мехатроника дсг 7; шток сцепления дсг 7; 0am325091f; замена штоков мехатроника dsg 7 dq200; установка мехатроника dsg 7 выставление штоков; штоки сцепления dsg; штоки сцепления dsg 7; штоки dsg 7 99 и 101; замена штоков мехатроника dsg 7; ремкомплект штоков мехатроника dsg 7; короткий шток dsg7; купить шток dsg7</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925476/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="n">
-        <v>2950</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>0am325477</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
-        </is>
-      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://basket-34.wbbasket.ru/vol7115/part711557/711557492/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>2447.15</v>
+        <v>2950</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-34.wbbasket.ru/vol7115/part711557/711557492/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="n">
+        <v>2447.15</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -2211,32 +2258,32 @@
 Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходников и подвержен большому износу</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6709/part670925/670925538/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="n">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n">
         <v>980</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
 Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
@@ -2265,32 +2312,32 @@
 шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-34.wbbasket.ru/vol7115/part711529/711529108/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="n">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="n">
         <v>1319.7</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Фильтр-сетка 123014-AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG-7 (DL501 / 0B5 / DQ500 / 0BH). Используется для тонкой фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими моделями с коробками DSG-7. Лёгкая установка, полный аналог оригинала 0B5 325 421. Отличный вариант для быстрого и недорогого восстановления работоспособности АКПП. Неоригинал высокого качества.
 Подходит для:
@@ -2304,32 +2351,32 @@
 Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501. Новая.</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-32.wbbasket.ru/vol6720/part672031/672031715/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="n">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n">
         <v>1225</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>31705-1XF0C</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Новое поколение Nissan Mitsubishi Renault</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E (Новое поколение) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
 Описание товара
@@ -2352,32 +2399,32 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-34.wbbasket.ru/vol7114/part711450/711450909/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="n">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="n">
         <v>40052</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>31705-1XF1A</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение Nissan Mitsubishi Renault</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF011E Старое поколение для вариатора CVT RE0F10A. Восстанавливает давление масла и стабильную работу трансмиссии. Прямая замена штатного узла без доработок.
 Гидроблок вариатора JF011E Старое поколение — управляющий узел CVT-коробки, отвечающий за распределение давления масла и работу соленоидов. Применяется в вариаторах RE0F10A и устанавливается на автомобили Nissan, Mitsubishi, Renault и Jeep.
@@ -2405,32 +2452,32 @@
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi ремонт вариатора jf011e</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>https://basket-34.wbbasket.ru/vol7114/part711439/711439292/images/big/1.webp</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="n">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n">
         <v>40052</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>31705-X428B</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mitsubishi</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый
 Краткое описание (первые 3 строки — самое важное для Ozon)
@@ -2464,32 +2511,32 @@
 гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-34.wbbasket.ru/vol7113/part711385/711385750/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="n">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="n">
         <v>42408</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mitsubishi</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -2512,85 +2559,54 @@
 гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>https://basket-34.wbbasket.ru/vol7114/part711424/711424704/images/big/1.webp</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="n">
-        <v>40052</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>55565480</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480 / 5636119</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet&lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии&lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
-        </is>
-      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670860/670860836/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="n">
-        <v>980</v>
+        <v>40052</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ250-ALU-KIT</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
+          <t>Импульсное кольцо распредвала GM 55565480 / 5636119</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
-Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet&lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии&lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://basket-38.wbbasket.ru/vol8379/part837943/837943386/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="n">
-        <v>2150</v>
+        <v>980</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DF-DQ500-FH-KIT</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2608,15 +2624,15 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://basket-38.wbbasket.ru/vol8379/part837952/837952965/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>1564.8</v>
+        <v>1515.9</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
     </row>
@@ -2636,7 +2652,11 @@
           <t>Тестовая карточка для проверки автоматизации</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="n">
         <v>100</v>
@@ -2664,7 +2684,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670862/670862930/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2684,7 +2704,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E/RE0F10A вариатора CVT, 4 шт NSK</t>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2694,7 +2714,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://basket-32.wbbasket.ru/vol6708/part670858/670858043/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
